--- a/public/downloads/CarlsonLiquidcrystal2024.xlsx
+++ b/public/downloads/CarlsonLiquidcrystal2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="58">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>H2O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>C16H26O2</t>
+  </si>
+  <si>
+    <t>H2O</t>
   </si>
   <si>
     <t>O</t>
@@ -179,10 +202,10 @@
     <t>OH</t>
   </si>
   <si>
-    <t>H</t>
+    <t>C16H25O2</t>
   </si>
   <si>
-    <t>C16H25O2</t>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -668,10 +691,10 @@
         <v>13</v>
       </c>
       <c r="N3" s="5">
-        <v>120.4422645568848</v>
+        <v>120442.2645568848</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03429449446380545</v>
+        <v>34.29449446380546</v>
       </c>
       <c r="P3" s="5">
         <v>3512</v>
@@ -718,10 +741,10 @@
         <v>13</v>
       </c>
       <c r="N4" s="5">
-        <v>97.6619336605072</v>
+        <v>97661.9336605072</v>
       </c>
       <c r="O4" s="4">
-        <v>0.0676797877065192</v>
+        <v>67.67978770651919</v>
       </c>
       <c r="P4" s="5">
         <v>1443</v>
@@ -768,10 +791,10 @@
         <v>13</v>
       </c>
       <c r="N5" s="5">
-        <v>230.4105682373047</v>
+        <v>230410.5682373047</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1580319398061075</v>
+        <v>158.0319398061075</v>
       </c>
       <c r="P5" s="5">
         <v>1458</v>
@@ -818,10 +841,10 @@
         <v>13</v>
       </c>
       <c r="N6" s="5">
-        <v>132.1356933116913</v>
+        <v>132135.6933116913</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08820807297175653</v>
+        <v>88.20807297175654</v>
       </c>
       <c r="P6" s="5">
         <v>1498</v>
@@ -868,10 +891,10 @@
         <v>13</v>
       </c>
       <c r="N7" s="5">
-        <v>314.3766701221466</v>
+        <v>314376.6701221466</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1926327635552369</v>
+        <v>192.6327635552369</v>
       </c>
       <c r="P7" s="5">
         <v>1632</v>
@@ -918,10 +941,10 @@
         <v>13</v>
       </c>
       <c r="N8" s="5">
-        <v>38.11118650436401</v>
+        <v>38111.18650436401</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02561235652175001</v>
+        <v>25.61235652175001</v>
       </c>
       <c r="P8" s="5">
         <v>1488</v>
@@ -968,10 +991,10 @@
         <v>13</v>
       </c>
       <c r="N9" s="5">
-        <v>148.2814269065857</v>
+        <v>148281.4269065857</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02934522598586695</v>
+        <v>29.34522598586695</v>
       </c>
       <c r="P9" s="5">
         <v>5053</v>
@@ -1018,10 +1041,10 @@
         <v>13</v>
       </c>
       <c r="N10" s="5">
-        <v>87.30112862586975</v>
+        <v>87301.12862586975</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08267152331995242</v>
+        <v>82.67152331995243</v>
       </c>
       <c r="P10" s="5">
         <v>1056</v>
@@ -1068,10 +1091,10 @@
         <v>13</v>
       </c>
       <c r="N11" s="5">
-        <v>63.63836932182312</v>
+        <v>63638.36932182312</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04055982748363487</v>
+        <v>40.55982748363488</v>
       </c>
       <c r="P11" s="5">
         <v>1569</v>
@@ -1118,10 +1141,10 @@
         <v>13</v>
       </c>
       <c r="N12" s="5">
-        <v>29.27045750617981</v>
+        <v>29270.45750617981</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02004825856587658</v>
+        <v>20.04825856587658</v>
       </c>
       <c r="P12" s="5">
         <v>1460</v>
@@ -1168,10 +1191,10 @@
         <v>13</v>
       </c>
       <c r="N13" s="5">
-        <v>139.3243598937988</v>
+        <v>139324.3598937988</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07141176826950221</v>
+        <v>71.41176826950222</v>
       </c>
       <c r="P13" s="5">
         <v>1951</v>
@@ -1218,10 +1241,10 @@
         <v>13</v>
       </c>
       <c r="N14" s="5">
-        <v>942.5551705360413</v>
+        <v>942555.1705360413</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3246831452070414</v>
+        <v>324.6831452070414</v>
       </c>
       <c r="P14" s="5">
         <v>2903</v>
@@ -1268,10 +1291,10 @@
         <v>13</v>
       </c>
       <c r="N15" s="5">
-        <v>376.5814518928528</v>
+        <v>376581.4518928528</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3107107688884924</v>
+        <v>310.7107688884924</v>
       </c>
       <c r="P15" s="5">
         <v>1212</v>
@@ -1318,10 +1341,10 @@
         <v>13</v>
       </c>
       <c r="N16" s="5">
-        <v>523.6777470111847</v>
+        <v>523677.7470111847</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1011742169650666</v>
+        <v>101.1742169650666</v>
       </c>
       <c r="P16" s="5">
         <v>5176</v>
@@ -1368,10 +1391,10 @@
         <v>13</v>
       </c>
       <c r="N17" s="5">
-        <v>155.8448345661163</v>
+        <v>155844.8345661163</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09888631634905859</v>
+        <v>98.88631634905859</v>
       </c>
       <c r="P17" s="5">
         <v>1576</v>
@@ -1399,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1410,9 +1433,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1446,8 +1475,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1469,34 +1506,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1303159047682326</v>
+        <v>0.3213825602627788</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1303159047682326</v>
+        <v>0.1195646659711151</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2829882944209352</v>
+        <v>0.3312752983135401</v>
       </c>
       <c r="E3" s="4">
-        <v>77.04081632653066</v>
+        <v>79.01360544217675</v>
       </c>
       <c r="F3" s="4">
-        <v>86.1372110365399</v>
+        <v>76.46532438478739</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1510,66 +1565,98 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3213825602627788</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1195646659711151</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1174118867038582</v>
+        <v>0.137244064131463</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1174118867038582</v>
+        <v>0.03715912585377623</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2100106556951786</v>
+        <v>0.3394162106017984</v>
       </c>
       <c r="E4" s="4">
-        <v>90.27210884353742</v>
+        <v>76.6666666666665</v>
       </c>
       <c r="F4" s="4">
-        <v>89.37360178970911</v>
+        <v>83.97091722595111</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.137244064131463</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03715912585377623</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3786008952742585</v>
+        <v>0.3297312161566707</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1616898976893326</v>
+        <v>0.09464310267939702</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1906688243834408</v>
+        <v>0.1251442904895956</v>
       </c>
       <c r="E5" s="4">
-        <v>86.56462585034004</v>
+        <v>85.51020408163259</v>
       </c>
       <c r="F5" s="4">
-        <v>86.72259507830006</v>
+        <v>87.15883668903832</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -1592,25 +1679,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3297312161566707</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09464310267939702</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2681444866687825</v>
+        <v>0.2746513656325673</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2681444866687825</v>
+        <v>0.2746513656325673</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2898561199228782</v>
+        <v>0.266676562913287</v>
       </c>
       <c r="E6" s="4">
-        <v>90.51020408163265</v>
+        <v>87.65306122448979</v>
       </c>
       <c r="F6" s="4">
-        <v>92.18120805369128</v>
+        <v>87.51677852348993</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -1633,25 +1736,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2746513656325673</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2746513656325673</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1322881671805476</v>
+        <v>1.123765716241167</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1322881671805476</v>
+        <v>1.123765716241167</v>
       </c>
       <c r="D7" s="4">
-        <v>0.148549947209915</v>
+        <v>0.9658176408649979</v>
       </c>
       <c r="E7" s="4">
-        <v>90</v>
+        <v>93.06122448979592</v>
       </c>
       <c r="F7" s="4">
-        <v>92.08053691275168</v>
+        <v>88.85906040268456</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -1674,25 +1793,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.123765716241167</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.123765716241167</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1208535340504682</v>
+        <v>0.1811531386409655</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1208535340504682</v>
+        <v>0.1811531386409655</v>
       </c>
       <c r="D8" s="4">
-        <v>0.09787796103805135</v>
+        <v>0.2192428978528369</v>
       </c>
       <c r="E8" s="4">
-        <v>100</v>
+        <v>83.87755102040816</v>
       </c>
       <c r="F8" s="4">
-        <v>98.75838926174497</v>
+        <v>82.78523489932886</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -1715,9 +1850,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1811531386409655</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1811531386409655</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1728,6 +1879,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1735,7 +1887,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1746,9 +1898,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1782,8 +1940,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1805,25 +1971,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1408727377327435</v>
+        <v>0.09226157646812301</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1005671555590801</v>
+        <v>0.02971529486330837</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2768529198974636</v>
+        <v>0.5143527426465084</v>
       </c>
       <c r="E3" s="4">
-        <v>71.19047619047606</v>
+        <v>64.04761904761874</v>
       </c>
       <c r="F3" s="4">
-        <v>82.62863534675625</v>
+        <v>66.74496644295246</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -1846,25 +2030,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09226157646812301</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02971529486330837</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1935504683138068</v>
+        <v>0.2934203559277305</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4380557489648709</v>
+        <v>0.2090094620776348</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2729688722038001</v>
+        <v>0.1842177651733425</v>
       </c>
       <c r="E4" s="4">
-        <v>71.57596371882069</v>
+        <v>58.9455782312925</v>
       </c>
       <c r="F4" s="4">
-        <v>78.90007457121565</v>
+        <v>78.60178970917252</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -1887,107 +2087,155 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2934203559277305</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2090094620776348</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.207617055335291</v>
+        <v>0.7171513925406856</v>
       </c>
       <c r="C5" s="4">
-        <v>0.207617055335291</v>
+        <v>0.2825694510852088</v>
       </c>
       <c r="D5" s="4">
-        <v>0.17132278243002</v>
+        <v>0.6306429595165971</v>
       </c>
       <c r="E5" s="4">
-        <v>94.14965986394557</v>
+        <v>57.66439909297084</v>
       </c>
       <c r="F5" s="4">
-        <v>94.92170022371367</v>
+        <v>68.25503355704647</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7171513925406856</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2825694510852088</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3244749416113279</v>
+        <v>0.2146181951760866</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3244749416113279</v>
+        <v>0.03613122502625288</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2723912109136961</v>
+        <v>0.2959303747415163</v>
       </c>
       <c r="E6" s="4">
-        <v>90.10204081632654</v>
+        <v>53.06122448979592</v>
       </c>
       <c r="F6" s="4">
-        <v>89.31208053691275</v>
+        <v>58.27740492170022</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2146181951760866</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.03613122502625288</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.3321884260180639</v>
+        <v>0.5601197125347426</v>
       </c>
       <c r="C7" s="4">
-        <v>0.3321884260180639</v>
+        <v>0.5601197125347426</v>
       </c>
       <c r="D7" s="4">
-        <v>0.3368113622668432</v>
+        <v>0.3551855923565199</v>
       </c>
       <c r="E7" s="4">
-        <v>91.12244897959184</v>
+        <v>91.32653061224489</v>
       </c>
       <c r="F7" s="4">
-        <v>93.48993288590604</v>
+        <v>85</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -2010,25 +2258,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.5601197125347426</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.5601197125347426</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.3278358818920424</v>
+        <v>0.1381583795550512</v>
       </c>
       <c r="C8" s="4">
-        <v>0.3278358818920424</v>
+        <v>0.1381583795550512</v>
       </c>
       <c r="D8" s="4">
-        <v>0.09913762826045058</v>
+        <v>0.1672883615496801</v>
       </c>
       <c r="E8" s="4">
-        <v>92.24489795918367</v>
+        <v>79.89795918367346</v>
       </c>
       <c r="F8" s="4">
-        <v>82.91946308724832</v>
+        <v>84.8993288590604</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -2051,9 +2315,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1381583795550512</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1381583795550512</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2064,6 +2344,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2071,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2082,9 +2363,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2118,8 +2405,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2141,107 +2436,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1383730513265</v>
+        <v>0.1174118867038582</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08194667765991603</v>
+        <v>0.1174118867038582</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2199726047526068</v>
+        <v>0.2100106556951786</v>
       </c>
       <c r="E3" s="4">
-        <v>75.90702947845811</v>
+        <v>90.27210884353742</v>
       </c>
       <c r="F3" s="4">
-        <v>85.05219985085742</v>
+        <v>89.37360178970911</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1174118867038582</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1174118867038582</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.405826674895839</v>
+        <v>0.1303159047682326</v>
       </c>
       <c r="C4" s="4">
-        <v>1.688522332167963</v>
+        <v>0.1303159047682326</v>
       </c>
       <c r="D4" s="4">
-        <v>1.510166274505214</v>
+        <v>0.2829882944209352</v>
       </c>
       <c r="E4" s="4">
-        <v>81.29251700680331</v>
+        <v>77.04081632653066</v>
       </c>
       <c r="F4" s="4">
-        <v>83.16927665920828</v>
+        <v>86.1372110365399</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1303159047682326</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1303159047682326</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.457568735836593</v>
+        <v>0.3786008952742585</v>
       </c>
       <c r="C5" s="4">
-        <v>0.258034652803957</v>
+        <v>0.1616898976893326</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2969661662565149</v>
+        <v>0.1906688243834408</v>
       </c>
       <c r="E5" s="4">
-        <v>87.89115646258499</v>
+        <v>86.56462585034004</v>
       </c>
       <c r="F5" s="4">
-        <v>89.80984340044778</v>
+        <v>86.72259507830006</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -2264,25 +2609,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3786008952742585</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1616898976893326</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3821283687353514</v>
+        <v>0.2681444866687825</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3821283687353514</v>
+        <v>0.2681444866687825</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3644935001135252</v>
+        <v>0.2898561199228782</v>
       </c>
       <c r="E6" s="4">
-        <v>92.48299319727892</v>
+        <v>90.51020408163265</v>
       </c>
       <c r="F6" s="4">
-        <v>94.14988814317672</v>
+        <v>92.18120805369128</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2305,25 +2666,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2681444866687825</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2681444866687825</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1621978864672826</v>
+        <v>0.1208535340504682</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1621978864672826</v>
+        <v>0.1208535340504682</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1653488264086889</v>
+        <v>0.09787796103805135</v>
       </c>
       <c r="E7" s="4">
-        <v>92.34693877551021</v>
+        <v>100</v>
       </c>
       <c r="F7" s="4">
-        <v>95.55928411633109</v>
+        <v>98.75838926174497</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -2346,25 +2723,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1208535340504682</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1208535340504682</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.06269756537358262</v>
+        <v>0.1322881671805476</v>
       </c>
       <c r="C8" s="4">
-        <v>0.06269756537358262</v>
+        <v>0.1322881671805476</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1635123847095201</v>
+        <v>0.148549947209915</v>
       </c>
       <c r="E8" s="4">
-        <v>97.95918367346938</v>
+        <v>90</v>
       </c>
       <c r="F8" s="4">
-        <v>94.92170022371366</v>
+        <v>92.08053691275168</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -2387,9 +2780,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1322881671805476</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1322881671805476</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2400,6 +2809,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2407,7 +2817,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2418,9 +2828,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2454,8 +2870,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2477,25 +2901,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9370392574983685</v>
+        <v>0.1935504683138068</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4195025498461895</v>
+        <v>0.4380557489648709</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8696210592659467</v>
+        <v>0.2729688722038001</v>
       </c>
       <c r="E3" s="4">
-        <v>64.86394557823105</v>
+        <v>71.57596371882069</v>
       </c>
       <c r="F3" s="4">
-        <v>79.97762863534693</v>
+        <v>78.90007457121565</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -2518,25 +2960,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1935504683138068</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4380557489648709</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3775544693098898</v>
+        <v>0.1408727377327435</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2956531000390896</v>
+        <v>0.1005671555590801</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3914200870475308</v>
+        <v>0.2768529198974636</v>
       </c>
       <c r="E4" s="4">
-        <v>75.21541950113355</v>
+        <v>71.19047619047606</v>
       </c>
       <c r="F4" s="4">
-        <v>75.32065622669613</v>
+        <v>82.62863534675625</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -2545,80 +3003,112 @@
         <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1408727377327435</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1005671555590801</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3726637472298222</v>
+        <v>0.207617055335291</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1528787079797382</v>
+        <v>0.207617055335291</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2164474437223352</v>
+        <v>0.17132278243002</v>
       </c>
       <c r="E5" s="4">
-        <v>76.54195011337876</v>
+        <v>94.14965986394557</v>
       </c>
       <c r="F5" s="4">
-        <v>81.3422818791948</v>
+        <v>94.92170022371367</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.207617055335291</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.207617055335291</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6110831607580565</v>
+        <v>0.3244749416113279</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6110831607580565</v>
+        <v>0.3244749416113279</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6113066781759642</v>
+        <v>0.2723912109136961</v>
       </c>
       <c r="E6" s="4">
-        <v>81.78571428571429</v>
+        <v>90.10204081632654</v>
       </c>
       <c r="F6" s="4">
-        <v>80.50335570469798</v>
+        <v>89.31208053691275</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2641,25 +3131,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3244749416113279</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3244749416113279</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2771375761035131</v>
+        <v>0.3278358818920424</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2771375761035131</v>
+        <v>0.3278358818920424</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2822814569476293</v>
+        <v>0.09913762826045058</v>
       </c>
       <c r="E7" s="4">
-        <v>88.9795918367347</v>
+        <v>92.24489795918367</v>
       </c>
       <c r="F7" s="4">
-        <v>91.61073825503355</v>
+        <v>82.91946308724832</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -2682,25 +3188,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3278358818920424</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3278358818920424</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.6025522591503432</v>
+        <v>0.3321884260180639</v>
       </c>
       <c r="C8" s="4">
-        <v>0.6025522591503432</v>
+        <v>0.3321884260180639</v>
       </c>
       <c r="D8" s="4">
-        <v>0.3362847210796645</v>
+        <v>0.3368113622668432</v>
       </c>
       <c r="E8" s="4">
-        <v>78.46938775510205</v>
+        <v>91.12244897959184</v>
       </c>
       <c r="F8" s="4">
-        <v>59.83221476510067</v>
+        <v>93.48993288590604</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -2723,9 +3245,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3321884260180639</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.3321884260180639</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2736,6 +3274,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2743,7 +3282,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2754,9 +3293,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2790,8 +3335,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2813,25 +3366,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4461259877564565</v>
+        <v>1.405826674895839</v>
       </c>
       <c r="C3" s="4">
-        <v>0.526818951681987</v>
+        <v>1.688522332167963</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6225788430255695</v>
+        <v>1.510166274505214</v>
       </c>
       <c r="E3" s="4">
-        <v>67.85714285714288</v>
+        <v>81.29251700680331</v>
       </c>
       <c r="F3" s="4">
-        <v>79.46308724832222</v>
+        <v>83.16927665920828</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -2854,25 +3425,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.405826674895839</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.688522332167963</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1781110634376972</v>
+        <v>0.1383730513265</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1982144050359622</v>
+        <v>0.08194667765991603</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2697162697685703</v>
+        <v>0.2199726047526068</v>
       </c>
       <c r="E4" s="4">
-        <v>71.58730158730131</v>
+        <v>75.90702947845811</v>
       </c>
       <c r="F4" s="4">
-        <v>78.87024608501125</v>
+        <v>85.05219985085742</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -2895,66 +3482,98 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1383730513265</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08194667765991603</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.03977575993404</v>
+        <v>0.457568735836593</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.258034652803957</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2260142391050695</v>
+        <v>0.2969661662565149</v>
       </c>
       <c r="E5" s="4">
-        <v>36.39455782312925</v>
+        <v>87.89115646258499</v>
       </c>
       <c r="F5" s="4">
-        <v>48.29977628635314</v>
+        <v>89.80984340044778</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.457568735836593</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.258034652803957</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2708773572445433</v>
+        <v>0.3821283687353514</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2708773572445433</v>
+        <v>0.3821283687353514</v>
       </c>
       <c r="D6" s="4">
-        <v>0.110562031053846</v>
+        <v>0.3644935001135252</v>
       </c>
       <c r="E6" s="4">
-        <v>66.98979591836735</v>
+        <v>92.48299319727892</v>
       </c>
       <c r="F6" s="4">
-        <v>80.28523489932886</v>
+        <v>94.14988814317672</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -2977,91 +3596,139 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3821283687353514</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3821283687353514</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.4786431207653834</v>
+        <v>0.06269756537358262</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>0.06269756537358262</v>
       </c>
       <c r="D7" s="4">
-        <v>1.137082920908625</v>
+        <v>0.1635123847095201</v>
       </c>
       <c r="E7" s="4">
-        <v>59.08163265306123</v>
+        <v>97.95918367346938</v>
       </c>
       <c r="F7" s="4">
-        <v>70.46979865771812</v>
+        <v>94.92170022371366</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.06269756537358262</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.06269756537358262</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>2.966780016007704</v>
+        <v>0.1621978864672826</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>0.1621978864672826</v>
       </c>
       <c r="D8" s="4">
-        <v>2.675575742306677</v>
+        <v>0.1653488264086889</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>92.34693877551021</v>
       </c>
       <c r="F8" s="4">
-        <v>0</v>
+        <v>95.55928411633109</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
       <c r="H8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
       </c>
       <c r="J8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1621978864672826</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1621978864672826</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3072,6 +3739,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3079,7 +3747,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3090,9 +3758,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3126,8 +3800,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3149,25 +3831,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.195606233091912</v>
+        <v>0.3775544693098898</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5132276351046734</v>
+        <v>0.2956531000390896</v>
       </c>
       <c r="D3" s="4">
-        <v>1.037114044991326</v>
+        <v>0.3914200870475308</v>
       </c>
       <c r="E3" s="4">
-        <v>65.78231292516982</v>
+        <v>75.21541950113355</v>
       </c>
       <c r="F3" s="4">
-        <v>77.15510812826307</v>
+        <v>75.32065622669613</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -3176,39 +3876,55 @@
         <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3775544693098898</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2956531000390896</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2796913546182462</v>
+        <v>0.9370392574983685</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2046244191878941</v>
+        <v>0.4195025498461895</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3345274567716245</v>
+        <v>0.8696210592659467</v>
       </c>
       <c r="E4" s="4">
-        <v>71.96145124716533</v>
+        <v>64.86394557823105</v>
       </c>
       <c r="F4" s="4">
-        <v>75.52199850857627</v>
+        <v>79.97762863534693</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -3231,66 +3947,98 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9370392574983685</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4195025498461895</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7611457019633528</v>
+        <v>0.3726637472298222</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7611457019633528</v>
+        <v>0.1528787079797382</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7775512645231165</v>
+        <v>0.2164474437223352</v>
       </c>
       <c r="E5" s="4">
-        <v>98.09523809523809</v>
+        <v>76.54195011337876</v>
       </c>
       <c r="F5" s="4">
-        <v>97.81879194630872</v>
+        <v>81.3422818791948</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3726637472298222</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1528787079797382</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.9760275442600559</v>
+        <v>0.6110831607580565</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9760275442600559</v>
+        <v>0.6110831607580565</v>
       </c>
       <c r="D6" s="4">
-        <v>0.9828658212423633</v>
+        <v>0.6113066781759642</v>
       </c>
       <c r="E6" s="4">
-        <v>95.91836734693878</v>
+        <v>81.78571428571429</v>
       </c>
       <c r="F6" s="4">
-        <v>96.59395973154362</v>
+        <v>80.50335570469798</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3313,25 +4061,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6110831607580565</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6110831607580565</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.2362644360068487</v>
+        <v>0.6025522591503432</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2362644360068487</v>
+        <v>0.6025522591503432</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2429944858554052</v>
+        <v>0.3362847210796645</v>
       </c>
       <c r="E7" s="4">
-        <v>95.81632653061224</v>
+        <v>78.46938775510205</v>
       </c>
       <c r="F7" s="4">
-        <v>95.36912751677852</v>
+        <v>59.83221476510067</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -3354,25 +4118,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.6025522591503432</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.6025522591503432</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.7686753926825531</v>
+        <v>0.2771375761035131</v>
       </c>
       <c r="C8" s="4">
-        <v>0.7686753926825531</v>
+        <v>0.2771375761035131</v>
       </c>
       <c r="D8" s="4">
-        <v>0.7870755551409445</v>
+        <v>0.2822814569476293</v>
       </c>
       <c r="E8" s="4">
-        <v>99.69387755102041</v>
+        <v>88.9795918367347</v>
       </c>
       <c r="F8" s="4">
-        <v>98.8255033557047</v>
+        <v>91.61073825503355</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -3395,9 +4175,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2771375761035131</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2771375761035131</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3408,6 +4204,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3415,7 +4212,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3426,9 +4223,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3462,8 +4265,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3485,34 +4296,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4862886479379836</v>
+        <v>0.1781110634376972</v>
       </c>
       <c r="C3" s="4">
-        <v>1.09684725593597</v>
+        <v>0.1982144050359622</v>
       </c>
       <c r="D3" s="4">
-        <v>0.545396093118395</v>
+        <v>0.2697162697685703</v>
       </c>
       <c r="E3" s="4">
-        <v>63.0272108843535</v>
+        <v>71.58730158730131</v>
       </c>
       <c r="F3" s="4">
-        <v>74.83221476510094</v>
+        <v>78.87024608501125</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -3526,25 +4355,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1781110634376972</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1982144050359622</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.260247992472685</v>
+        <v>0.4461259877564565</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3664541475532346</v>
+        <v>0.526818951681987</v>
       </c>
       <c r="D4" s="4">
-        <v>0.276117848353555</v>
+        <v>0.6225788430255695</v>
       </c>
       <c r="E4" s="4">
-        <v>65.30612244897921</v>
+        <v>67.85714285714288</v>
       </c>
       <c r="F4" s="4">
-        <v>77.8411633109623</v>
+        <v>79.46308724832222</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -3567,25 +4412,39 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4461259877564565</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.526818951681987</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.0596075692556</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>1.03977575993404</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.2823781707665966</v>
+        <v>0.2260142391050695</v>
       </c>
       <c r="E5" s="4">
-        <v>6.235827664399109</v>
+        <v>36.39455782312925</v>
       </c>
       <c r="F5" s="4">
-        <v>17.54287844891893</v>
+        <v>48.29977628635314</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -3600,74 +4459,102 @@
         <v>3</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.03977575993404</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.716180023633783</v>
+        <v>0.2708773572445433</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>0.2708773572445433</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1641753659480263</v>
+        <v>0.110562031053846</v>
       </c>
       <c r="E6" s="4">
-        <v>18.50340136054422</v>
+        <v>66.98979591836735</v>
       </c>
       <c r="F6" s="4">
-        <v>33.84228187919464</v>
+        <v>80.28523489932886</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2708773572445433</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2708773572445433</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.8363283737894847</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
+        <v>2.966780016007704</v>
+      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4">
-        <v>1.368267582297022</v>
+        <v>2.675575742306677</v>
       </c>
       <c r="E7" s="4">
-        <v>37.44897959183673</v>
+        <v>0</v>
       </c>
       <c r="F7" s="4">
-        <v>56.47651006711409</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -3690,25 +4577,37 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2.966780016007704</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1824164630800738</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
+        <v>0.4786431207653834</v>
+      </c>
+      <c r="C8" s="4"/>
       <c r="D8" s="4">
-        <v>0.4467002840664804</v>
+        <v>1.137082920908625</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>59.08163265306123</v>
       </c>
       <c r="F8" s="4">
-        <v>0</v>
+        <v>70.46979865771812</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -3731,9 +4630,23 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.4786431207653834</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3744,6 +4657,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3751,7 +4665,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3762,9 +4676,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3798,8 +4718,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3821,34 +4749,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.17489326140459</v>
+        <v>0.2796913546182462</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.2046244191878941</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8378837321318701</v>
+        <v>0.3345274567716245</v>
       </c>
       <c r="E3" s="4">
-        <v>59.39909297052138</v>
+        <v>71.96145124716533</v>
       </c>
       <c r="F3" s="4">
-        <v>63.10589112602535</v>
+        <v>75.52199850857627</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
@@ -3862,66 +4808,98 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2796913546182462</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2046244191878941</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5089718143256287</v>
+        <v>1.195606233091912</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6682283811337939</v>
+        <v>0.5132276351046734</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5532553235799705</v>
+        <v>1.037114044991326</v>
       </c>
       <c r="E4" s="4">
-        <v>73.36734693877528</v>
+        <v>65.78231292516982</v>
       </c>
       <c r="F4" s="4">
-        <v>81.38702460850158</v>
+        <v>77.15510812826307</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.195606233091912</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5132276351046734</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6577307094719487</v>
+        <v>0.7611457019633528</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6577307094719487</v>
+        <v>0.7611457019633528</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6366558978544153</v>
+        <v>0.7775512645231165</v>
       </c>
       <c r="E5" s="4">
-        <v>95.47619047619047</v>
+        <v>98.09523809523809</v>
       </c>
       <c r="F5" s="4">
-        <v>94.38478747203574</v>
+        <v>97.81879194630872</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -3944,25 +4922,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7611457019633528</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7611457019633528</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.7859891463518451</v>
+        <v>0.9760275442600559</v>
       </c>
       <c r="C6" s="4">
-        <v>0.7859891463518451</v>
+        <v>0.9760275442600559</v>
       </c>
       <c r="D6" s="4">
-        <v>0.7451396543979953</v>
+        <v>0.9828658212423633</v>
       </c>
       <c r="E6" s="4">
-        <v>89.5748299319728</v>
+        <v>95.91836734693878</v>
       </c>
       <c r="F6" s="4">
-        <v>85.83892617449665</v>
+        <v>96.59395973154362</v>
       </c>
       <c r="G6" s="5">
         <v>2</v>
@@ -3985,25 +4979,41 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9760275442600559</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.9760275442600559</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1549175963404821</v>
+        <v>0.7686753926825531</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1549175963404821</v>
+        <v>0.7686753926825531</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1566923544409917</v>
+        <v>0.7870755551409445</v>
       </c>
       <c r="E7" s="4">
-        <v>90.91836734693878</v>
+        <v>99.69387755102041</v>
       </c>
       <c r="F7" s="4">
-        <v>92.71812080536913</v>
+        <v>98.8255033557047</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -4026,25 +5036,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.7686753926825531</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.7686753926825531</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>1.209482407387185</v>
+        <v>0.2362644360068487</v>
       </c>
       <c r="C8" s="4">
-        <v>1.209482407387185</v>
+        <v>0.2362644360068487</v>
       </c>
       <c r="D8" s="4">
-        <v>1.271356767233328</v>
+        <v>0.2429944858554052</v>
       </c>
       <c r="E8" s="4">
-        <v>98.67346938775511</v>
+        <v>95.81632653061224</v>
       </c>
       <c r="F8" s="4">
-        <v>96.82326621923939</v>
+        <v>95.36912751677852</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -4067,9 +5093,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2362644360068487</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2362644360068487</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4080,12 +5122,1780 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.260247992472685</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3664541475532346</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.276117848353555</v>
+      </c>
+      <c r="E3" s="4">
+        <v>65.30612244897921</v>
+      </c>
+      <c r="F3" s="4">
+        <v>77.8411633109623</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.260247992472685</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3664541475532346</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4862886479379836</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.09684725593597</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.545396093118395</v>
+      </c>
+      <c r="E4" s="4">
+        <v>63.0272108843535</v>
+      </c>
+      <c r="F4" s="4">
+        <v>74.83221476510094</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4862886479379836</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.09684725593597</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.0596075692556</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.2823781707665966</v>
+      </c>
+      <c r="E5" s="4">
+        <v>6.235827664399109</v>
+      </c>
+      <c r="F5" s="4">
+        <v>17.54287844891893</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.0596075692556</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.716180023633783</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>0.1641753659480263</v>
+      </c>
+      <c r="E6" s="4">
+        <v>18.50340136054422</v>
+      </c>
+      <c r="F6" s="4">
+        <v>33.84228187919464</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.716180023633783</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.1824164630800738</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
+        <v>0.4467002840664804</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1824164630800738</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.8363283737894847</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
+        <v>1.368267582297022</v>
+      </c>
+      <c r="E8" s="4">
+        <v>37.44897959183673</v>
+      </c>
+      <c r="F8" s="4">
+        <v>56.47651006711409</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.8363283737894847</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5089718143256287</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6682283811337939</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5532553235799705</v>
+      </c>
+      <c r="E3" s="4">
+        <v>73.36734693877528</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.38702460850158</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5089718143256287</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6682283811337939</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.17489326140459</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>0.8378837321318701</v>
+      </c>
+      <c r="E4" s="4">
+        <v>59.39909297052138</v>
+      </c>
+      <c r="F4" s="4">
+        <v>63.10589112602535</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.17489326140459</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6577307094719487</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6577307094719487</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6366558978544153</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.47619047619047</v>
+      </c>
+      <c r="F5" s="4">
+        <v>94.38478747203574</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6577307094719487</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6577307094719487</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.7859891463518451</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.7859891463518451</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.7451396543979953</v>
+      </c>
+      <c r="E6" s="4">
+        <v>89.5748299319728</v>
+      </c>
+      <c r="F6" s="4">
+        <v>85.83892617449665</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.7859891463518451</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7859891463518451</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.209482407387185</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.209482407387185</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.271356767233328</v>
+      </c>
+      <c r="E7" s="4">
+        <v>98.67346938775511</v>
+      </c>
+      <c r="F7" s="4">
+        <v>96.82326621923939</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.209482407387185</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.209482407387185</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.1549175963404821</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1549175963404821</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.1566923544409917</v>
+      </c>
+      <c r="E8" s="4">
+        <v>90.91836734693878</v>
+      </c>
+      <c r="F8" s="4">
+        <v>92.71812080536913</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1549175963404821</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1549175963404821</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D3" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="E3" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="F3" s="3">
+        <v>61.53846153846154</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.8397136669523674</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3087616331966198</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.4303301957055168</v>
+      </c>
+      <c r="K3" s="4">
+        <v>54.38513867085337</v>
+      </c>
+      <c r="L3" s="4">
+        <v>61.78884873515841</v>
+      </c>
+      <c r="M3" s="5">
+        <v>13</v>
+      </c>
+      <c r="N3" s="5">
+        <v>120442.2645568848</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.29449446380546</v>
+      </c>
+      <c r="P3" s="5">
+        <v>3512</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.43914947979116</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.5220787660980781</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3995576660787216</v>
+      </c>
+      <c r="K4" s="4">
+        <v>86.14599686028247</v>
+      </c>
+      <c r="L4" s="4">
+        <v>85.77267251763871</v>
+      </c>
+      <c r="M4" s="5">
+        <v>13</v>
+      </c>
+      <c r="N4" s="5">
+        <v>97661.9336605072</v>
+      </c>
+      <c r="O4" s="4">
+        <v>67.67978770651919</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D5" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.4045822877814447</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2648060950063194</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3523497994393499</v>
+      </c>
+      <c r="K5" s="4">
+        <v>81.81318681318623</v>
+      </c>
+      <c r="L5" s="4">
+        <v>84.69454482877174</v>
+      </c>
+      <c r="M5" s="5">
+        <v>13</v>
+      </c>
+      <c r="N5" s="5">
+        <v>230410.5682373047</v>
+      </c>
+      <c r="O5" s="4">
+        <v>158.0319398061075</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C6" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3248808849668939</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2505840667418804</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2491135437980731</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.83673469387776</v>
+      </c>
+      <c r="L6" s="4">
+        <v>86.37153674066396</v>
+      </c>
+      <c r="M6" s="5">
+        <v>13</v>
+      </c>
+      <c r="N6" s="5">
+        <v>132135.6933116913</v>
+      </c>
+      <c r="O6" s="4">
+        <v>88.20807297175654</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.296605866892746</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2693050185263345</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3379144899865711</v>
+      </c>
+      <c r="K7" s="4">
+        <v>84.52642595499753</v>
+      </c>
+      <c r="L7" s="4">
+        <v>88.68869385647862</v>
+      </c>
+      <c r="M7" s="5">
+        <v>13</v>
+      </c>
+      <c r="N7" s="5">
+        <v>314376.6701221466</v>
+      </c>
+      <c r="O7" s="4">
+        <v>192.6327635552369</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C8" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="D8" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3245611621384619</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2577551388113408</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.3158400817507086</v>
+      </c>
+      <c r="K8" s="4">
+        <v>82.75510204081638</v>
+      </c>
+      <c r="L8" s="4">
+        <v>83.80485286525504</v>
+      </c>
+      <c r="M8" s="5">
+        <v>13</v>
+      </c>
+      <c r="N8" s="5">
+        <v>38111.18650436401</v>
+      </c>
+      <c r="O8" s="4">
+        <v>25.61235652175001</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.341231881327045</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2092839208570331</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3924596234921982</v>
+      </c>
+      <c r="K9" s="4">
+        <v>63.02459445316583</v>
+      </c>
+      <c r="L9" s="4">
+        <v>71.32765444845901</v>
+      </c>
+      <c r="M9" s="5">
+        <v>13</v>
+      </c>
+      <c r="N9" s="5">
+        <v>148281.4269065857</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.34522598586695</v>
+      </c>
+      <c r="P9" s="5">
+        <v>5053</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.205262825754433</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1546661536969599</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2213187285840297</v>
+      </c>
+      <c r="K10" s="4">
+        <v>87.12715855573006</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.37704353811674</v>
+      </c>
+      <c r="M10" s="5">
+        <v>13</v>
+      </c>
+      <c r="N10" s="5">
+        <v>87301.12862586975</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.67152331995243</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2257765365598682</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2744942512958429</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2418588566114259</v>
+      </c>
+      <c r="K11" s="4">
+        <v>82.6399790685503</v>
+      </c>
+      <c r="L11" s="4">
+        <v>86.49113749784881</v>
+      </c>
+      <c r="M11" s="5">
+        <v>13</v>
+      </c>
+      <c r="N11" s="5">
+        <v>63638.36932182312</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.55982748363488</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5380351981144896</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.504615951457524</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.5491664113760206</v>
+      </c>
+      <c r="K12" s="4">
+        <v>85.42647828362038</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.68267079676602</v>
+      </c>
+      <c r="M12" s="5">
+        <v>13</v>
+      </c>
+      <c r="N12" s="5">
+        <v>29270.45750617981</v>
+      </c>
+      <c r="O12" s="4">
+        <v>20.04825856587658</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>61.53846153846154</v>
+      </c>
+      <c r="C13" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D13" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.5510483522218623</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3903461528268406</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.4825881003451277</v>
+      </c>
+      <c r="K13" s="4">
+        <v>75.45264259549955</v>
+      </c>
+      <c r="L13" s="4">
+        <v>78.64395112717206</v>
+      </c>
+      <c r="M13" s="5">
+        <v>13</v>
+      </c>
+      <c r="N13" s="5">
+        <v>139324.3598937988</v>
+      </c>
+      <c r="O13" s="4">
+        <v>71.41176826950222</v>
+      </c>
+      <c r="P13" s="5">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>53.84615384615385</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6907089449728272</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3319702379874975</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5683623677708171</v>
+      </c>
+      <c r="K14" s="4">
+        <v>55.42909471480945</v>
+      </c>
+      <c r="L14" s="4">
+        <v>65.45689210118927</v>
+      </c>
+      <c r="M14" s="5">
+        <v>13</v>
+      </c>
+      <c r="N14" s="5">
+        <v>942555.1705360413</v>
+      </c>
+      <c r="O14" s="4">
+        <v>324.6831452070414</v>
+      </c>
+      <c r="P14" s="5">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.7435634450946189</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.6620315641546822</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.726413844795329</v>
+      </c>
+      <c r="K15" s="4">
+        <v>84.22030350601763</v>
+      </c>
+      <c r="L15" s="4">
+        <v>87.60540354500054</v>
+      </c>
+      <c r="M15" s="5">
+        <v>13</v>
+      </c>
+      <c r="N15" s="5">
+        <v>376581.4518928528</v>
+      </c>
+      <c r="O15" s="4">
+        <v>310.7107688884924</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="C16" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D16" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="E16" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="F16" s="3">
+        <v>61.53846153846154</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.6053490394719946</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.6099185170141462</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.419614994998092</v>
+      </c>
+      <c r="K16" s="4">
+        <v>36.78178963893276</v>
+      </c>
+      <c r="L16" s="4">
+        <v>48.8315264154192</v>
+      </c>
+      <c r="M16" s="5">
+        <v>13</v>
+      </c>
+      <c r="N16" s="5">
+        <v>523677.7470111847</v>
+      </c>
+      <c r="O16" s="4">
+        <v>101.1742169650666</v>
+      </c>
+      <c r="P16" s="5">
+        <v>5176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C17" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D17" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.76624351169522</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.6940030207905323</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.692439483936083</v>
+      </c>
+      <c r="K17" s="4">
+        <v>81.03610675039238</v>
+      </c>
+      <c r="L17" s="4">
+        <v>82.9117191533293</v>
+      </c>
+      <c r="M17" s="5">
+        <v>13</v>
+      </c>
+      <c r="N17" s="5">
+        <v>155844.8345661163</v>
+      </c>
+      <c r="O17" s="4">
+        <v>98.88631634905859</v>
+      </c>
+      <c r="P17" s="5">
+        <v>1576</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4208,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -4774,13 +7584,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -4840,9 +7650,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>7</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>7</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>7</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>4</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>9</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>7</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4853,9 +8418,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4889,8 +8460,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4912,34 +8491,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4055141816210899</v>
+        <v>0.2937549360872443</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.4772403192773709</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3687700638842735</v>
+        <v>0.429629366425786</v>
       </c>
       <c r="E3" s="4">
-        <v>48.50340136054427</v>
+        <v>52.16553287981851</v>
       </c>
       <c r="F3" s="4">
-        <v>69.14988814317668</v>
+        <v>65.10812826249106</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
@@ -4953,34 +8550,48 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2937549360872443</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4772403192773709</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2937549360872443</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4772403192773709</v>
-      </c>
+        <v>0.4055141816210899</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.429629366425786</v>
+        <v>0.3687700638842735</v>
       </c>
       <c r="E4" s="4">
-        <v>52.16553287981851</v>
+        <v>48.50340136054427</v>
       </c>
       <c r="F4" s="4">
-        <v>65.10812826249106</v>
+        <v>69.14988814317668</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -4994,10 +8605,24 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4055141816210899</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.63924809337361</v>
@@ -5035,10 +8660,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.63924809337361</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1989283135021935</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.170075443469841</v>
@@ -5076,67 +8717,93 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.170075443469841</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.250116266810295</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
+        <v>1.22317441720088</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
+        <v>0.4365816952617934</v>
+      </c>
+      <c r="E7" s="4">
+        <v>49.89795918367347</v>
+      </c>
+      <c r="F7" s="4">
+        <v>49.66442953020134</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.22317441720088</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.3374007329943822</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
         <v>0.3456884012225316</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="4">
         <v>64.79591836734694</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F8" s="4">
         <v>77.7628635346756</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.22317441720088</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.4365816952617934</v>
-      </c>
-      <c r="E8" s="4">
-        <v>49.89795918367347</v>
-      </c>
-      <c r="F8" s="4">
-        <v>49.66442953020134</v>
-      </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -5158,9 +8825,23 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3374007329943822</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5171,14 +8852,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5189,9 +8871,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5225,8 +8913,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5248,25 +8944,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2606949219775352</v>
+        <v>0.1316709924023485</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1227772767138653</v>
+        <v>0.0440861240234085</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2096029860188828</v>
+        <v>0.1761974104524787</v>
       </c>
       <c r="E3" s="4">
-        <v>76.53061224489795</v>
+        <v>83.29931972789113</v>
       </c>
       <c r="F3" s="4">
-        <v>79.27665920954564</v>
+        <v>78.89261744966444</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -5289,25 +9003,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1316709924023485</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0440861240234085</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1316709924023485</v>
+        <v>0.2606949219775352</v>
       </c>
       <c r="C4" s="4">
-        <v>0.0440861240234085</v>
+        <v>0.1227772767138653</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1761974104524787</v>
+        <v>0.2096029860188828</v>
       </c>
       <c r="E4" s="4">
-        <v>83.29931972789113</v>
+        <v>76.53061224489795</v>
       </c>
       <c r="F4" s="4">
-        <v>78.89261744966444</v>
+        <v>79.27665920954564</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -5330,10 +9060,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2606949219775352</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1227772767138653</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7692072282645626</v>
@@ -5371,10 +9117,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7692072282645626</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7692072282645626</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.2046232492559739</v>
@@ -5412,67 +9174,99 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2046232492559739</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2046232492559739</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
+        <v>1.456476056757765</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.456476056757765</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.14504417199214</v>
+      </c>
+      <c r="E7" s="4">
+        <v>86.83673469387755</v>
+      </c>
+      <c r="F7" s="4">
+        <v>77.24832214765101</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.456476056757765</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.456476056757765</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.3585012540820287</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C8" s="4">
         <v>0.3585012540820287</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D8" s="4">
         <v>0.37388974285156</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="4">
         <v>90.81632653061224</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F8" s="4">
         <v>93.32214765100672</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.456476056757765</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1.456476056757765</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1.14504417199214</v>
-      </c>
-      <c r="E8" s="4">
-        <v>86.83673469387755</v>
-      </c>
-      <c r="F8" s="4">
-        <v>77.24832214765101</v>
-      </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -5494,9 +9288,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3585012540820287</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.3585012540820287</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5507,14 +9317,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5525,9 +9336,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,8 +9378,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5584,25 +9409,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4586667676441027</v>
+        <v>0.3549033060696161</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1418380813362017</v>
+        <v>0.2263313673373659</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4136339385978533</v>
+        <v>0.2623603526037073</v>
       </c>
       <c r="E3" s="4">
-        <v>74.55782312925174</v>
+        <v>78.80952380952347</v>
       </c>
       <c r="F3" s="4">
-        <v>83.46756152125275</v>
+        <v>77.3340790454875</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
@@ -5611,39 +9454,55 @@
         <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3549033060696161</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2263313673373659</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3549033060696161</v>
+        <v>0.4586667676441027</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2263313673373659</v>
+        <v>0.1418380813362017</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2623603526037073</v>
+        <v>0.4136339385978533</v>
       </c>
       <c r="E4" s="4">
-        <v>78.80952380952347</v>
+        <v>74.55782312925174</v>
       </c>
       <c r="F4" s="4">
-        <v>77.3340790454875</v>
+        <v>83.46756152125275</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
@@ -5652,24 +9511,40 @@
         <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4586667676441027</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1418380813362017</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4004733870016016</v>
@@ -5707,10 +9582,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4004733870016016</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4004733870016016</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.5183704231381796</v>
@@ -5748,67 +9639,99 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5183704231381796</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1296033789747923</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
+        <v>0.2173982502849867</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.2173982502849867</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.1679135503204634</v>
+      </c>
+      <c r="E7" s="4">
+        <v>97.55102040816327</v>
+      </c>
+      <c r="F7" s="4">
+        <v>97.04697986577182</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2173982502849867</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2173982502849867</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.3633002624514745</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C8" s="4">
         <v>0.3633002624514745</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D8" s="4">
         <v>0.371741680860822</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="4">
         <v>89.18367346938776</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F8" s="4">
         <v>93.28859060402685</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.2173982502849867</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.2173982502849867</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.1679135503204634</v>
-      </c>
-      <c r="E8" s="4">
-        <v>97.55102040816327</v>
-      </c>
-      <c r="F8" s="4">
-        <v>97.04697986577182</v>
-      </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -5830,9 +9753,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3633002624514745</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.3633002624514745</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5843,14 +9782,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5861,9 +9801,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5897,8 +9843,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5920,34 +9874,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3891384218253542</v>
+        <v>0.2142065892643169</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1343679250012197</v>
+        <v>0.2142065892643169</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2956814179492149</v>
+        <v>0.2256397017122443</v>
       </c>
       <c r="E3" s="4">
-        <v>63.49206349206364</v>
+        <v>84.93197278911566</v>
       </c>
       <c r="F3" s="4">
-        <v>79.12751677852351</v>
+        <v>87.29306487695749</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -5961,34 +9933,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2142065892643169</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2142065892643169</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2142065892643169</v>
+        <v>0.3891384218253542</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2142065892643169</v>
+        <v>0.1343679250012197</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2256397017122443</v>
+        <v>0.2956814179492149</v>
       </c>
       <c r="E4" s="4">
-        <v>84.93197278911566</v>
+        <v>63.49206349206364</v>
       </c>
       <c r="F4" s="4">
-        <v>87.29306487695749</v>
+        <v>79.12751677852351</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -6002,10 +9990,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3891384218253542</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1343679250012197</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2959413268945307</v>
@@ -6043,10 +10047,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2959413268945307</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1597383128741399</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.2698698152304075</v>
@@ -6084,67 +10104,99 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2698698152304075</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2698698152304075</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
+        <v>0.6707106472881605</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.6707106472881605</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.5395696999462416</v>
+      </c>
+      <c r="E7" s="4">
+        <v>92.95918367346938</v>
+      </c>
+      <c r="F7" s="4">
+        <v>87.34899328859061</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.6707106472881605</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.6707106472881605</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.3151422128680395</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C8" s="4">
         <v>0.3151422128680395</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D8" s="4">
         <v>0.3218935117724584</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="4">
         <v>88.46938775510205</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F8" s="4">
         <v>92.78523489932886</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.6707106472881605</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.6707106472881605</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.5395696999462416</v>
-      </c>
-      <c r="E8" s="4">
-        <v>92.95918367346938</v>
-      </c>
-      <c r="F8" s="4">
-        <v>87.34899328859061</v>
-      </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -6166,9 +10218,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3151422128680395</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.3151422128680395</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6179,14 +10247,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6197,9 +10266,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -6233,8 +10308,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6256,92 +10339,142 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08371543312174741</v>
+        <v>0.1904656497916714</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0607216889453106</v>
+        <v>0.2006122572949209</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3137830041259792</v>
+        <v>0.285110832083338</v>
       </c>
       <c r="E3" s="4">
-        <v>67.23356009070281</v>
+        <v>89.35374149659862</v>
       </c>
       <c r="F3" s="4">
-        <v>82.56897837434767</v>
+        <v>88.93736017897079</v>
       </c>
       <c r="G3" s="5">
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1904656497916714</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2006122572949209</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1904656497916714</v>
+        <v>0.08371543312174741</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2006122572949209</v>
+        <v>0.0607216889453106</v>
       </c>
       <c r="D4" s="4">
-        <v>0.285110832083338</v>
+        <v>0.3137830041259792</v>
       </c>
       <c r="E4" s="4">
-        <v>89.35374149659862</v>
+        <v>67.23356009070281</v>
       </c>
       <c r="F4" s="4">
-        <v>88.93736017897079</v>
+        <v>82.56897837434767</v>
       </c>
       <c r="G4" s="5">
         <v>3</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08371543312174741</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0607216889453106</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5729506124641972</v>
@@ -6379,10 +10512,26 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5729506124641972</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3236588898645039</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.48343647611145</v>
@@ -6420,67 +10569,99 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>2</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.48343647611145</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.48343647611145</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
+        <v>0.186353051844435</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.186353051844435</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.1622289063366225</v>
+      </c>
+      <c r="E7" s="4">
+        <v>98.9795918367347</v>
+      </c>
+      <c r="F7" s="4">
+        <v>97.4496644295302</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.186353051844435</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.186353051844435</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.161255179405515</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C8" s="4">
         <v>0.161255179405515</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D8" s="4">
         <v>0.1703265295031713</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="4">
         <v>90</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F8" s="4">
         <v>92.95302013422818</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.186353051844435</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.186353051844435</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.1622289063366225</v>
-      </c>
-      <c r="E8" s="4">
-        <v>98.9795918367347</v>
-      </c>
-      <c r="F8" s="4">
-        <v>97.4496644295302</v>
-      </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -6502,9 +10683,25 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.161255179405515</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.161255179405515</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6515,678 +10712,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.137244064131463</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.03715912585377623</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3394162106017984</v>
-      </c>
-      <c r="E3" s="4">
-        <v>76.6666666666665</v>
-      </c>
-      <c r="F3" s="4">
-        <v>83.97091722595111</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3213825602627788</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1195646659711151</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3312752983135401</v>
-      </c>
-      <c r="E4" s="4">
-        <v>79.01360544217675</v>
-      </c>
-      <c r="F4" s="4">
-        <v>76.46532438478739</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3297312161566707</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.09464310267939702</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1251442904895956</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.51020408163259</v>
-      </c>
-      <c r="F5" s="4">
-        <v>87.15883668903832</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2746513656325673</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.2746513656325673</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.266676562913287</v>
-      </c>
-      <c r="E6" s="4">
-        <v>87.65306122448979</v>
-      </c>
-      <c r="F6" s="4">
-        <v>87.51677852348993</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.1811531386409655</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.1811531386409655</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2192428978528369</v>
-      </c>
-      <c r="E7" s="4">
-        <v>83.87755102040816</v>
-      </c>
-      <c r="F7" s="4">
-        <v>82.78523489932886</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.123765716241167</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1.123765716241167</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.9658176408649979</v>
-      </c>
-      <c r="E8" s="4">
-        <v>93.06122448979592</v>
-      </c>
-      <c r="F8" s="4">
-        <v>88.85906040268456</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2934203559277305</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2090094620776348</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1842177651733425</v>
-      </c>
-      <c r="E3" s="4">
-        <v>58.9455782312925</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.60178970917252</v>
-      </c>
-      <c r="G3" s="5">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.09226157646812301</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.02971529486330837</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5143527426465084</v>
-      </c>
-      <c r="E4" s="4">
-        <v>64.04761904761874</v>
-      </c>
-      <c r="F4" s="4">
-        <v>66.74496644295246</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7171513925406856</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2825694510852088</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6306429595165971</v>
-      </c>
-      <c r="E5" s="4">
-        <v>57.66439909297084</v>
-      </c>
-      <c r="F5" s="4">
-        <v>68.25503355704647</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.2146181951760866</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.03613122502625288</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.2959303747415163</v>
-      </c>
-      <c r="E6" s="4">
-        <v>53.06122448979592</v>
-      </c>
-      <c r="F6" s="4">
-        <v>58.27740492170022</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.1381583795550512</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.1381583795550512</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.1672883615496801</v>
-      </c>
-      <c r="E7" s="4">
-        <v>79.89795918367346</v>
-      </c>
-      <c r="F7" s="4">
-        <v>84.8993288590604</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.5601197125347426</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.5601197125347426</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.3551855923565199</v>
-      </c>
-      <c r="E8" s="4">
-        <v>91.32653061224489</v>
-      </c>
-      <c r="F8" s="4">
-        <v>85</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
